--- a/DMart_Retail_dataset.xlsx
+++ b/DMart_Retail_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA78B82E-ED09-4814-9CFB-171E649E8DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD7F4DE-5125-425F-BCBD-91CE57405E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1739,7 +1739,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -42944,6 +42975,50 @@
       <c r="Z1000" s="5"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="top10" dxfId="2" priority="2" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="top10" dxfId="0" priority="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/DMart_Retail_dataset.xlsx
+++ b/DMart_Retail_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD7F4DE-5125-425F-BCBD-91CE57405E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01FA087-3C7B-4839-AF87-0851363AF74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2420" yWindow="2420" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1739,7 +1739,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1747,16 +1747,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -42975,7 +42965,21 @@
       <c r="Z1000" s="5"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="top10" dxfId="1" priority="2" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="top10" dxfId="0" priority="1" rank="10"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -42986,7 +42990,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -42995,30 +43009,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="top10" dxfId="2" priority="2" rank="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="top10" dxfId="0" priority="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
